--- a/mystkdatav2/stock_inventory.xlsx
+++ b/mystkdatav2/stock_inventory.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -748,14 +748,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-07-18 16:06:34</t>
+          <t>2025-07-18 18:07:42</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1000</v>
+        <v>84</v>
       </c>
       <c r="F108" t="n">
         <v>18.25</v>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>84</v>
+        <v>1000</v>
       </c>
       <c r="F109" t="n">
         <v>18.25</v>
@@ -4672,12 +4672,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>00934</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>中信成長高股息</t>
+          <t>群益ESG投等債20+</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>643</v>
+        <v>3000</v>
       </c>
       <c r="F117" t="n">
-        <v>15.26</v>
+        <v>15.39</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
@@ -4701,12 +4701,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00934</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>群益ESG投等債20+</t>
+          <t>中信成長高股息</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3000</v>
+        <v>643</v>
       </c>
       <c r="F118" t="n">
-        <v>15.39</v>
+        <v>15.26</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>124</v>
+        <v>1000</v>
       </c>
       <c r="F126" t="n">
         <v>17.67</v>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1000</v>
+        <v>124</v>
       </c>
       <c r="F127" t="n">
         <v>17.67</v>
@@ -5988,7 +5988,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">

--- a/mystkdatav2/stock_inventory.xlsx
+++ b/mystkdatav2/stock_inventory.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-07-18 18:07:42</t>
+          <t>2025-07-21 08:50:42</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>84</v>
+        <v>1000</v>
       </c>
       <c r="F108" t="n">
         <v>18.25</v>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1000</v>
+        <v>84</v>
       </c>
       <c r="F109" t="n">
         <v>18.25</v>
@@ -4672,12 +4672,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00934</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>群益ESG投等債20+</t>
+          <t>中信成長高股息</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3000</v>
+        <v>643</v>
       </c>
       <c r="F117" t="n">
-        <v>15.39</v>
+        <v>15.26</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
@@ -4701,12 +4701,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>00934</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>中信成長高股息</t>
+          <t>群益ESG投等債20+</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>643</v>
+        <v>3000</v>
       </c>
       <c r="F118" t="n">
-        <v>15.26</v>
+        <v>15.39</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1000</v>
+        <v>124</v>
       </c>
       <c r="F126" t="n">
         <v>17.67</v>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>124</v>
+        <v>1000</v>
       </c>
       <c r="F127" t="n">
         <v>17.67</v>

--- a/mystkdatav2/stock_inventory.xlsx
+++ b/mystkdatav2/stock_inventory.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4525,10 +4525,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2025-07-23 14:53:22</t>
-        </is>
+      <c r="A146" s="3" t="n">
+        <v>45861.62039351852</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -4560,6 +4558,267 @@
       <c r="I146" t="inlineStr">
         <is>
           <t>修正測試 (調整-100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n">
+        <v>45862.3537037037</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>00878</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>國泰高股息</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>買入</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>705</v>
+      </c>
+      <c r="F147" t="n">
+        <v>21</v>
+      </c>
+      <c r="G147" t="n">
+        <v>14805</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>庫存調整 (調整+705)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="n">
+        <v>45862.35445601852</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>00934</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>中信成長高股息</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>買入</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>8726</v>
+      </c>
+      <c r="F148" t="n">
+        <v>18</v>
+      </c>
+      <c r="G148" t="n">
+        <v>157068</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>庫存調整 (調整+8726)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>45862.35490740741</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>買入</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>468</v>
+      </c>
+      <c r="F149" t="n">
+        <v>15</v>
+      </c>
+      <c r="G149" t="n">
+        <v>7020</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>庫存調整 (調整+468)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n">
+        <v>45862.35517361111</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>買入</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>711</v>
+      </c>
+      <c r="F150" t="n">
+        <v>14</v>
+      </c>
+      <c r="G150" t="n">
+        <v>9954</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>庫存調整 (調整+711)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>45862.35585648148</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>買入</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>2920</v>
+      </c>
+      <c r="F151" t="n">
+        <v>50</v>
+      </c>
+      <c r="G151" t="n">
+        <v>146000</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>庫存調整 (調整+2920)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="n">
+        <v>45862.35665509259</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2464</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>星宇航空</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>買入</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F152" t="n">
+        <v>20</v>
+      </c>
+      <c r="G152" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>庫存調整 (調整+1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2025-07-24 08:34:11</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>買入</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>8</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G153" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>庫存調整 (調整+8)</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4617,497 +4876,497 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21982</v>
+        <v>2920</v>
       </c>
       <c r="D2" t="n">
-        <v>24.92</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>547775.5699999999</v>
+        <v>146000</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>45861.62039351852</v>
+        <v>45862.35585648148</v>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00687B</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>國泰20年美債</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5000</v>
+        <v>21982</v>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>24.92</v>
       </c>
       <c r="E3" t="n">
-        <v>155000</v>
+        <v>547775.5699999999</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>45367.43071759259</v>
+        <v>45861.62039351852</v>
       </c>
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00687B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>元大高息低波</t>
+          <t>國泰20年美債</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24269</v>
+        <v>5000</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="E4" t="n">
-        <v>1213450</v>
+        <v>155000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>45824.43071759259</v>
+        <v>45367.43071759259</v>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00751B</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>元大AAA-A公司債</t>
+          <t>元大高息低波</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>52000</v>
+        <v>24269</v>
       </c>
       <c r="D5" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E5" t="n">
-        <v>1768000</v>
+        <v>1213450</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>45338.43071759259</v>
+        <v>45824.43071759259</v>
       </c>
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00857B</t>
+          <t>00751B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>永豐20年美債</t>
+          <t>元大AAA-A公司債</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57000</v>
+        <v>52000</v>
       </c>
       <c r="D6" t="n">
-        <v>25.97</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
-        <v>1480180</v>
+        <v>1768000</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>45665.43071759259</v>
+        <v>45338.43071759259</v>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00878</t>
+          <t>00857B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>國泰高股息</t>
+          <t>永豐20年美債</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>58347</v>
+        <v>57000</v>
       </c>
       <c r="D7" t="n">
-        <v>20.02</v>
+        <v>25.97</v>
       </c>
       <c r="E7" t="n">
-        <v>1168010</v>
+        <v>1480180</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>45829.43071759259</v>
+        <v>45665.43071759259</v>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00934</t>
+          <t>00878</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中信成長高股息</t>
+          <t>國泰高股息</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50903</v>
+        <v>59052</v>
       </c>
       <c r="D8" t="n">
-        <v>18.73</v>
+        <v>20.03</v>
       </c>
       <c r="E8" t="n">
-        <v>953416.2</v>
+        <v>1182815</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>45852</v>
+        <v>45862.3537037037</v>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00934</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>群益ESG投等債20+</t>
+          <t>中信成長高股息</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>171000</v>
+        <v>59629</v>
       </c>
       <c r="D9" t="n">
-        <v>15.77</v>
+        <v>18.62</v>
       </c>
       <c r="E9" t="n">
-        <v>2695965</v>
+        <v>1110484.2</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>45756</v>
+        <v>45862.35445601852</v>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00948B</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>中信優息投資債</t>
+          <t>群益ESG投等債20+</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>160000</v>
+        <v>171000</v>
       </c>
       <c r="D10" t="n">
-        <v>10.27</v>
+        <v>15.77</v>
       </c>
       <c r="E10" t="n">
-        <v>1643200</v>
+        <v>2695965</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>45390.43071759259</v>
+        <v>45756</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00959B</t>
+          <t>00948B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>大華投等美債15Y+</t>
+          <t>中信優息投資債</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25000</v>
+        <v>160000</v>
       </c>
       <c r="D11" t="n">
-        <v>9.81</v>
+        <v>10.27</v>
       </c>
       <c r="E11" t="n">
-        <v>245350</v>
+        <v>1643200</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>45663</v>
+        <v>45390.43071759259</v>
       </c>
       <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>00959B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>大華投等美債15Y+</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>670</v>
+        <v>25000</v>
       </c>
       <c r="D12" t="n">
-        <v>156.8</v>
+        <v>9.81</v>
       </c>
       <c r="E12" t="n">
-        <v>105056</v>
+        <v>245350</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>45760.43071759259</v>
+        <v>45663</v>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11800</v>
+        <v>670</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>156.8</v>
       </c>
       <c r="E13" t="n">
-        <v>448400</v>
+        <v>105056</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>44939.43071759259</v>
+        <v>45760.43071759259</v>
       </c>
       <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2000</v>
+        <v>11800</v>
       </c>
       <c r="D14" t="n">
-        <v>140.5</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
-        <v>281000</v>
+        <v>448400</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>45854.43071759259</v>
+        <v>44939.43071759259</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12178</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="E15" t="n">
-        <v>158314</v>
+        <v>8000</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>45612.43071759259</v>
+        <v>45862.35707175926</v>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台新金</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17777</v>
+        <v>2000</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>140.5</v>
       </c>
       <c r="E16" t="n">
-        <v>231101</v>
+        <v>281000</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>44939.43071759259</v>
+        <v>45854.43071759259</v>
       </c>
       <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>星宇航空</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15602</v>
+        <v>1000</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>171622</v>
+        <v>20000</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>44939.43071759259</v>
+        <v>45862.35665509259</v>
       </c>
       <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>遠百</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2000</v>
+        <v>12178</v>
       </c>
       <c r="D18" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>42000</v>
+        <v>158314</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>45732.43071759259</v>
+        <v>45612.43071759259</v>
       </c>
       <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>全台</t>
+          <t>台新金</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4000</v>
+        <v>18488</v>
       </c>
       <c r="D19" t="n">
-        <v>26.85</v>
+        <v>13.04</v>
       </c>
       <c r="E19" t="n">
-        <v>107400</v>
+        <v>241055</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>45428.43071759259</v>
+        <v>45862.35517361111</v>
       </c>
       <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>佳醫</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1050</v>
+        <v>16070</v>
       </c>
       <c r="D20" t="n">
-        <v>80</v>
+        <v>11.12</v>
       </c>
       <c r="E20" t="n">
-        <v>84000</v>
+        <v>178642</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>45732.43071759259</v>
+        <v>45862.35490740741</v>
       </c>
       <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>臻頂KY</t>
+          <t>遠百</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D21" t="n">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>103000</v>
+        <v>42000</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>45732.43071759259</v>
@@ -5117,72 +5376,72 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>豐祥KY</t>
+          <t>全台</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="D22" t="n">
-        <v>194</v>
+        <v>26.85</v>
       </c>
       <c r="E22" t="n">
-        <v>388000</v>
+        <v>107400</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>45824.43071759259</v>
+        <v>45428.43071759259</v>
       </c>
       <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中租KY</t>
+          <t>佳醫</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13809</v>
+        <v>1050</v>
       </c>
       <c r="D23" t="n">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="E23" t="n">
-        <v>2292294</v>
+        <v>84000</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>45824.43071759259</v>
+        <v>45732.43071759259</v>
       </c>
       <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>臻頂KY</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2300</v>
+        <v>1000</v>
       </c>
       <c r="D24" t="n">
-        <v>207</v>
+        <v>103</v>
       </c>
       <c r="E24" t="n">
-        <v>476100</v>
+        <v>103000</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>45732.43071759259</v>
@@ -5192,52 +5451,127 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>豐祥KY</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="D25" t="n">
-        <v>400</v>
+        <v>194</v>
       </c>
       <c r="E25" t="n">
-        <v>4000</v>
+        <v>388000</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>45732.43071759259</v>
+        <v>45824.43071759259</v>
       </c>
       <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>5871</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>中租KY</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>13809</v>
+      </c>
+      <c r="D26" t="n">
+        <v>166</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2292294</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>45824.43071759259</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6605</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>帝寶</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D27" t="n">
+        <v>207</v>
+      </c>
+      <c r="E27" t="n">
+        <v>476100</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>45732.43071759259</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>群聯</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>400</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>45732.43071759259</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>9942</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>茂順</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C29" t="n">
         <v>1000</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D29" t="n">
         <v>132</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E29" t="n">
         <v>132000</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>45276.43071759259</v>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
